--- a/03_Outputs/Agroindustrial_Occidente/02_Demografia/demografia.xlsx
+++ b/03_Outputs/Agroindustrial_Occidente/02_Demografia/demografia.xlsx
@@ -112,7 +112,7 @@
     <numFmt numFmtId="251" formatCode="0.00"/>
     <numFmt numFmtId="252" formatCode="0.00"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,23 +122,140 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -158,7 +275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
@@ -181,76 +298,97 @@
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="180" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="181" xfId="0"/>
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="182" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="183" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="184" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="184" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="185" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="186" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="186" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="187" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="188" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="188" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="189" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="190" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="190" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="191" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="192" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="192" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="193" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="194" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="194" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="195" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="196" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="196" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="197" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="198" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="198" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="199" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="200" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="200" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="201" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="202" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="202" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="203" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="204" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="204" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="205" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="206" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="206" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="207" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="208" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="208" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="209" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="210" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="210" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="211" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="212" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="212" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="213" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="214" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="214" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="215" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="216" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="216" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="217" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="218" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="218" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="219" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="220" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="220" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="221" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="222" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="222" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="223" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="224" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="224" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="225" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="226" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="226" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="227" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="228" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="228" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="229" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="230" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="230" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="231" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="232" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="232" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="233" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="234" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="234" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="235" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="236" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="236" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="237" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="238" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="238" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="239" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="240" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="4" numFmtId="240" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="241" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="242" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="242" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="243" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="244" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="244" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="245" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="246" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="6" numFmtId="246" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="7" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="247" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="248" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="248" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="249" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="250" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="250" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="251" xfId="0"/>
-    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="252" xfId="0"/>
+    <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="8" numFmtId="252" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="6" fontId="9" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="7" fontId="10" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="8" fontId="11" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="9" fontId="12" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="10" fontId="13" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="11" fontId="14" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -579,19 +717,19 @@
   <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
-    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="29.711"/>
-    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="46.711"/>
-    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="8" max="8" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="9" max="9" bestFit="1" customWidth="1" hidden="false" width="48.711"/>
+    <col min="10" max="10" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="11" max="11" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
+    <col min="12" max="12" bestFit="1" customWidth="1" hidden="false" width="47.711"/>
+    <col min="13" max="13" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1114,28 +1252,28 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
+    <col min="1" max="2" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="112" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="112" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="112" t="inlineStr">
         <is>
           <t>Población total</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="112" t="inlineStr">
         <is>
           <t>Densidad poblacional (hab/km²)</t>
         </is>
@@ -1249,185 +1387,185 @@
   <dimension ref="A1:AG8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
-    <col min="8" max="14" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
-    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="17" max="23" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="24" max="24" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="25" max="25" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
-    <col min="26" max="32" bestFit="1" customWidth="1" hidden="false" width="15.711"/>
-    <col min="33" max="33" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="45.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="6.711"/>
+    <col min="8" max="14" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
+    <col min="15" max="15" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="16" max="16" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="17" max="23" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="24" max="24" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="25" max="25" bestFit="1" customWidth="1" hidden="false" width="14.711"/>
+    <col min="26" max="32" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="33" max="33" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="23" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="23" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="23" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="23" t="inlineStr">
         <is>
           <t>Población masculina</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="23" t="inlineStr">
         <is>
           <t>Población femenina</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
         <is>
           <t>0 a 9</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="23" t="inlineStr">
         <is>
           <t>10 a 19</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="23" t="inlineStr">
         <is>
           <t>20 a 29</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="23" t="inlineStr">
         <is>
           <t>30 a 39</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="23" t="inlineStr">
         <is>
           <t>40 a 49</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="23" t="inlineStr">
         <is>
           <t>50 a 59</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="23" t="inlineStr">
         <is>
           <t>60 a 69</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="23" t="inlineStr">
         <is>
           <t>70 a 79</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="23" t="inlineStr">
         <is>
           <t>80 o más</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="23" t="inlineStr">
         <is>
           <t>Hombres 0 a 9</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="Q1" s="23" t="inlineStr">
         <is>
           <t>Hombres 10 a 19</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="R1" s="23" t="inlineStr">
         <is>
           <t>Hombres 20 a 29</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="S1" s="23" t="inlineStr">
         <is>
           <t>Hombres 30 a 39</t>
         </is>
       </c>
-      <c r="T1" s="2" t="inlineStr">
+      <c r="T1" s="23" t="inlineStr">
         <is>
           <t>Hombres 40 a 49</t>
         </is>
       </c>
-      <c r="U1" s="2" t="inlineStr">
+      <c r="U1" s="23" t="inlineStr">
         <is>
           <t>Hombres 50 a 59</t>
         </is>
       </c>
-      <c r="V1" s="2" t="inlineStr">
+      <c r="V1" s="23" t="inlineStr">
         <is>
           <t>Hombres 60 a 69</t>
         </is>
       </c>
-      <c r="W1" s="2" t="inlineStr">
+      <c r="W1" s="23" t="inlineStr">
         <is>
           <t>Hombres 70 a 79</t>
         </is>
       </c>
-      <c r="X1" s="2" t="inlineStr">
+      <c r="X1" s="23" t="inlineStr">
         <is>
           <t>Hombres 80 o más</t>
         </is>
       </c>
-      <c r="Y1" s="2" t="inlineStr">
+      <c r="Y1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 0 a 9</t>
         </is>
       </c>
-      <c r="Z1" s="2" t="inlineStr">
+      <c r="Z1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 10 a 19</t>
         </is>
       </c>
-      <c r="AA1" s="2" t="inlineStr">
+      <c r="AA1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 20 a 29</t>
         </is>
       </c>
-      <c r="AB1" s="2" t="inlineStr">
+      <c r="AB1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 30 a 39</t>
         </is>
       </c>
-      <c r="AC1" s="2" t="inlineStr">
+      <c r="AC1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 40 a 49</t>
         </is>
       </c>
-      <c r="AD1" s="2" t="inlineStr">
+      <c r="AD1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 50 a 59</t>
         </is>
       </c>
-      <c r="AE1" s="2" t="inlineStr">
+      <c r="AE1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 60 a 69</t>
         </is>
       </c>
-      <c r="AF1" s="2" t="inlineStr">
+      <c r="AF1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 70 a 79</t>
         </is>
       </c>
-      <c r="AG1" s="2" t="inlineStr">
+      <c r="AG1" s="23" t="inlineStr">
         <is>
           <t>Mujeres 80 o más</t>
         </is>
@@ -1452,91 +1590,91 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E2" s="22">
+      <c r="E2" s="25">
         <v>1574</v>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="27">
         <v>1298</v>
       </c>
-      <c r="G2" s="26">
+      <c r="G2" s="29">
         <v>403</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="31">
         <v>414</v>
       </c>
-      <c r="I2" s="30">
+      <c r="I2" s="33">
         <v>375</v>
       </c>
-      <c r="J2" s="32">
+      <c r="J2" s="35">
         <v>421</v>
       </c>
-      <c r="K2" s="34">
+      <c r="K2" s="37">
         <v>382</v>
       </c>
-      <c r="L2" s="36">
+      <c r="L2" s="39">
         <v>320</v>
       </c>
-      <c r="M2" s="38">
+      <c r="M2" s="41">
         <v>277</v>
       </c>
-      <c r="N2" s="40">
+      <c r="N2" s="43">
         <v>194</v>
       </c>
-      <c r="O2" s="42">
+      <c r="O2" s="45">
         <v>86</v>
       </c>
-      <c r="P2" s="44">
+      <c r="P2" s="47">
         <v>218</v>
       </c>
-      <c r="Q2" s="46">
+      <c r="Q2" s="49">
         <v>241</v>
       </c>
-      <c r="R2" s="48">
+      <c r="R2" s="51">
         <v>213</v>
       </c>
-      <c r="S2" s="50">
+      <c r="S2" s="53">
         <v>224</v>
       </c>
-      <c r="T2" s="52">
+      <c r="T2" s="55">
         <v>197</v>
       </c>
-      <c r="U2" s="54">
+      <c r="U2" s="57">
         <v>174</v>
       </c>
-      <c r="V2" s="56">
+      <c r="V2" s="59">
         <v>166</v>
       </c>
-      <c r="W2" s="58">
+      <c r="W2" s="61">
         <v>100</v>
       </c>
-      <c r="X2" s="60">
+      <c r="X2" s="63">
         <v>41</v>
       </c>
-      <c r="Y2" s="62">
+      <c r="Y2" s="65">
         <v>185</v>
       </c>
-      <c r="Z2" s="64">
+      <c r="Z2" s="67">
         <v>173</v>
       </c>
-      <c r="AA2" s="66">
+      <c r="AA2" s="69">
         <v>162</v>
       </c>
-      <c r="AB2" s="68">
+      <c r="AB2" s="71">
         <v>197</v>
       </c>
-      <c r="AC2" s="70">
+      <c r="AC2" s="73">
         <v>185</v>
       </c>
-      <c r="AD2" s="72">
+      <c r="AD2" s="75">
         <v>146</v>
       </c>
-      <c r="AE2" s="74">
+      <c r="AE2" s="77">
         <v>111</v>
       </c>
-      <c r="AF2" s="76">
+      <c r="AF2" s="79">
         <v>94</v>
       </c>
-      <c r="AG2" s="78">
+      <c r="AG2" s="81">
         <v>45</v>
       </c>
     </row>
@@ -1559,91 +1697,91 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="25">
         <v>8279</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="27">
         <v>8208</v>
       </c>
-      <c r="G3" s="26">
+      <c r="G3" s="29">
         <v>2429</v>
       </c>
-      <c r="H3" s="28">
+      <c r="H3" s="31">
         <v>2561</v>
       </c>
-      <c r="I3" s="30">
+      <c r="I3" s="33">
         <v>2224</v>
       </c>
-      <c r="J3" s="32">
+      <c r="J3" s="35">
         <v>2264</v>
       </c>
-      <c r="K3" s="34">
+      <c r="K3" s="37">
         <v>2037</v>
       </c>
-      <c r="L3" s="36">
+      <c r="L3" s="39">
         <v>1732</v>
       </c>
-      <c r="M3" s="38">
+      <c r="M3" s="41">
         <v>1670</v>
       </c>
-      <c r="N3" s="40">
+      <c r="N3" s="43">
         <v>1052</v>
       </c>
-      <c r="O3" s="42">
+      <c r="O3" s="45">
         <v>518</v>
       </c>
-      <c r="P3" s="44">
+      <c r="P3" s="47">
         <v>1211</v>
       </c>
-      <c r="Q3" s="46">
+      <c r="Q3" s="49">
         <v>1264</v>
       </c>
-      <c r="R3" s="48">
+      <c r="R3" s="51">
         <v>1094</v>
       </c>
-      <c r="S3" s="50">
+      <c r="S3" s="53">
         <v>1145</v>
       </c>
-      <c r="T3" s="52">
+      <c r="T3" s="55">
         <v>1057</v>
       </c>
-      <c r="U3" s="54">
+      <c r="U3" s="57">
         <v>880</v>
       </c>
-      <c r="V3" s="56">
+      <c r="V3" s="59">
         <v>850</v>
       </c>
-      <c r="W3" s="58">
+      <c r="W3" s="61">
         <v>536</v>
       </c>
-      <c r="X3" s="60">
+      <c r="X3" s="63">
         <v>242</v>
       </c>
-      <c r="Y3" s="62">
+      <c r="Y3" s="65">
         <v>1218</v>
       </c>
-      <c r="Z3" s="64">
+      <c r="Z3" s="67">
         <v>1297</v>
       </c>
-      <c r="AA3" s="66">
+      <c r="AA3" s="69">
         <v>1130</v>
       </c>
-      <c r="AB3" s="68">
+      <c r="AB3" s="71">
         <v>1119</v>
       </c>
-      <c r="AC3" s="70">
+      <c r="AC3" s="73">
         <v>980</v>
       </c>
-      <c r="AD3" s="72">
+      <c r="AD3" s="75">
         <v>852</v>
       </c>
-      <c r="AE3" s="74">
+      <c r="AE3" s="77">
         <v>820</v>
       </c>
-      <c r="AF3" s="76">
+      <c r="AF3" s="79">
         <v>516</v>
       </c>
-      <c r="AG3" s="78">
+      <c r="AG3" s="81">
         <v>276</v>
       </c>
     </row>
@@ -1666,91 +1804,91 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="25">
         <v>12515</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="27">
         <v>12250</v>
       </c>
-      <c r="G4" s="26">
+      <c r="G4" s="29">
         <v>5707</v>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="31">
         <v>4465</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="33">
         <v>3600</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="35">
         <v>3341</v>
       </c>
-      <c r="K4" s="34">
+      <c r="K4" s="37">
         <v>2621</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="39">
         <v>1930</v>
       </c>
-      <c r="M4" s="38">
+      <c r="M4" s="41">
         <v>1566</v>
       </c>
-      <c r="N4" s="40">
+      <c r="N4" s="43">
         <v>1052</v>
       </c>
-      <c r="O4" s="42">
+      <c r="O4" s="45">
         <v>483</v>
       </c>
-      <c r="P4" s="44">
+      <c r="P4" s="47">
         <v>2944</v>
       </c>
-      <c r="Q4" s="46">
+      <c r="Q4" s="49">
         <v>2265</v>
       </c>
-      <c r="R4" s="48">
+      <c r="R4" s="51">
         <v>1797</v>
       </c>
-      <c r="S4" s="50">
+      <c r="S4" s="53">
         <v>1675</v>
       </c>
-      <c r="T4" s="52">
+      <c r="T4" s="55">
         <v>1325</v>
       </c>
-      <c r="U4" s="54">
+      <c r="U4" s="57">
         <v>953</v>
       </c>
-      <c r="V4" s="56">
+      <c r="V4" s="59">
         <v>810</v>
       </c>
-      <c r="W4" s="58">
+      <c r="W4" s="61">
         <v>512</v>
       </c>
-      <c r="X4" s="60">
+      <c r="X4" s="63">
         <v>234</v>
       </c>
-      <c r="Y4" s="62">
+      <c r="Y4" s="65">
         <v>2763</v>
       </c>
-      <c r="Z4" s="64">
+      <c r="Z4" s="67">
         <v>2200</v>
       </c>
-      <c r="AA4" s="66">
+      <c r="AA4" s="69">
         <v>1803</v>
       </c>
-      <c r="AB4" s="68">
+      <c r="AB4" s="71">
         <v>1666</v>
       </c>
-      <c r="AC4" s="70">
+      <c r="AC4" s="73">
         <v>1296</v>
       </c>
-      <c r="AD4" s="72">
+      <c r="AD4" s="75">
         <v>977</v>
       </c>
-      <c r="AE4" s="74">
+      <c r="AE4" s="77">
         <v>756</v>
       </c>
-      <c r="AF4" s="76">
+      <c r="AF4" s="79">
         <v>540</v>
       </c>
-      <c r="AG4" s="78">
+      <c r="AG4" s="81">
         <v>249</v>
       </c>
     </row>
@@ -1773,91 +1911,91 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="25">
         <v>10962</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="27">
         <v>11087</v>
       </c>
-      <c r="G5" s="26">
+      <c r="G5" s="29">
         <v>4415</v>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="31">
         <v>3616</v>
       </c>
-      <c r="I5" s="30">
+      <c r="I5" s="33">
         <v>3025</v>
       </c>
-      <c r="J5" s="32">
+      <c r="J5" s="35">
         <v>2912</v>
       </c>
-      <c r="K5" s="34">
+      <c r="K5" s="37">
         <v>2567</v>
       </c>
-      <c r="L5" s="36">
+      <c r="L5" s="39">
         <v>2120</v>
       </c>
-      <c r="M5" s="38">
+      <c r="M5" s="41">
         <v>1807</v>
       </c>
-      <c r="N5" s="40">
+      <c r="N5" s="43">
         <v>1122</v>
       </c>
-      <c r="O5" s="42">
+      <c r="O5" s="45">
         <v>465</v>
       </c>
-      <c r="P5" s="44">
+      <c r="P5" s="47">
         <v>2243</v>
       </c>
-      <c r="Q5" s="46">
+      <c r="Q5" s="49">
         <v>1868</v>
       </c>
-      <c r="R5" s="48">
+      <c r="R5" s="51">
         <v>1524</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="53">
         <v>1406</v>
       </c>
-      <c r="T5" s="52">
+      <c r="T5" s="55">
         <v>1280</v>
       </c>
-      <c r="U5" s="54">
+      <c r="U5" s="57">
         <v>1025</v>
       </c>
-      <c r="V5" s="56">
+      <c r="V5" s="59">
         <v>902</v>
       </c>
-      <c r="W5" s="58">
+      <c r="W5" s="61">
         <v>495</v>
       </c>
-      <c r="X5" s="60">
+      <c r="X5" s="63">
         <v>219</v>
       </c>
-      <c r="Y5" s="62">
+      <c r="Y5" s="65">
         <v>2172</v>
       </c>
-      <c r="Z5" s="64">
+      <c r="Z5" s="67">
         <v>1748</v>
       </c>
-      <c r="AA5" s="66">
+      <c r="AA5" s="69">
         <v>1501</v>
       </c>
-      <c r="AB5" s="68">
+      <c r="AB5" s="71">
         <v>1506</v>
       </c>
-      <c r="AC5" s="70">
+      <c r="AC5" s="73">
         <v>1287</v>
       </c>
-      <c r="AD5" s="72">
+      <c r="AD5" s="75">
         <v>1095</v>
       </c>
-      <c r="AE5" s="74">
+      <c r="AE5" s="77">
         <v>905</v>
       </c>
-      <c r="AF5" s="76">
+      <c r="AF5" s="79">
         <v>627</v>
       </c>
-      <c r="AG5" s="78">
+      <c r="AG5" s="81">
         <v>246</v>
       </c>
     </row>
@@ -1880,91 +2018,91 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E6" s="22">
+      <c r="E6" s="25">
         <v>4592</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="27">
         <v>4125</v>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="29">
         <v>1610</v>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="31">
         <v>1496</v>
       </c>
-      <c r="I6" s="30">
+      <c r="I6" s="33">
         <v>1257</v>
       </c>
-      <c r="J6" s="32">
+      <c r="J6" s="35">
         <v>1227</v>
       </c>
-      <c r="K6" s="34">
+      <c r="K6" s="37">
         <v>1079</v>
       </c>
-      <c r="L6" s="36">
+      <c r="L6" s="39">
         <v>726</v>
       </c>
-      <c r="M6" s="38">
+      <c r="M6" s="41">
         <v>584</v>
       </c>
-      <c r="N6" s="40">
+      <c r="N6" s="43">
         <v>488</v>
       </c>
-      <c r="O6" s="42">
+      <c r="O6" s="45">
         <v>250</v>
       </c>
-      <c r="P6" s="44">
+      <c r="P6" s="47">
         <v>849</v>
       </c>
-      <c r="Q6" s="46">
+      <c r="Q6" s="49">
         <v>813</v>
       </c>
-      <c r="R6" s="48">
+      <c r="R6" s="51">
         <v>678</v>
       </c>
-      <c r="S6" s="50">
+      <c r="S6" s="53">
         <v>664</v>
       </c>
-      <c r="T6" s="52">
+      <c r="T6" s="55">
         <v>550</v>
       </c>
-      <c r="U6" s="54">
+      <c r="U6" s="57">
         <v>362</v>
       </c>
-      <c r="V6" s="56">
+      <c r="V6" s="59">
         <v>298</v>
       </c>
-      <c r="W6" s="58">
+      <c r="W6" s="61">
         <v>251</v>
       </c>
-      <c r="X6" s="60">
+      <c r="X6" s="63">
         <v>127</v>
       </c>
-      <c r="Y6" s="62">
+      <c r="Y6" s="65">
         <v>761</v>
       </c>
-      <c r="Z6" s="64">
+      <c r="Z6" s="67">
         <v>683</v>
       </c>
-      <c r="AA6" s="66">
+      <c r="AA6" s="69">
         <v>579</v>
       </c>
-      <c r="AB6" s="68">
+      <c r="AB6" s="71">
         <v>563</v>
       </c>
-      <c r="AC6" s="70">
+      <c r="AC6" s="73">
         <v>529</v>
       </c>
-      <c r="AD6" s="72">
+      <c r="AD6" s="75">
         <v>364</v>
       </c>
-      <c r="AE6" s="74">
+      <c r="AE6" s="77">
         <v>286</v>
       </c>
-      <c r="AF6" s="76">
+      <c r="AF6" s="79">
         <v>237</v>
       </c>
-      <c r="AG6" s="78">
+      <c r="AG6" s="81">
         <v>123</v>
       </c>
     </row>
@@ -1987,200 +2125,200 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="25">
         <v>3752</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="27">
         <v>3577</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="29">
         <v>1309</v>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="31">
         <v>1171</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="33">
         <v>1020</v>
       </c>
-      <c r="J7" s="32">
+      <c r="J7" s="35">
         <v>1019</v>
       </c>
-      <c r="K7" s="34">
+      <c r="K7" s="37">
         <v>832</v>
       </c>
-      <c r="L7" s="36">
+      <c r="L7" s="39">
         <v>700</v>
       </c>
-      <c r="M7" s="38">
+      <c r="M7" s="41">
         <v>666</v>
       </c>
-      <c r="N7" s="40">
+      <c r="N7" s="43">
         <v>407</v>
       </c>
-      <c r="O7" s="42">
+      <c r="O7" s="45">
         <v>205</v>
       </c>
-      <c r="P7" s="44">
+      <c r="P7" s="47">
         <v>673</v>
       </c>
-      <c r="Q7" s="46">
+      <c r="Q7" s="49">
         <v>607</v>
       </c>
-      <c r="R7" s="48">
+      <c r="R7" s="51">
         <v>518</v>
       </c>
-      <c r="S7" s="50">
+      <c r="S7" s="53">
         <v>512</v>
       </c>
-      <c r="T7" s="52">
+      <c r="T7" s="55">
         <v>441</v>
       </c>
-      <c r="U7" s="54">
+      <c r="U7" s="57">
         <v>351</v>
       </c>
-      <c r="V7" s="56">
+      <c r="V7" s="59">
         <v>350</v>
       </c>
-      <c r="W7" s="58">
+      <c r="W7" s="61">
         <v>197</v>
       </c>
-      <c r="X7" s="60">
+      <c r="X7" s="63">
         <v>103</v>
       </c>
-      <c r="Y7" s="62">
+      <c r="Y7" s="65">
         <v>636</v>
       </c>
-      <c r="Z7" s="64">
+      <c r="Z7" s="67">
         <v>564</v>
       </c>
-      <c r="AA7" s="66">
+      <c r="AA7" s="69">
         <v>502</v>
       </c>
-      <c r="AB7" s="68">
+      <c r="AB7" s="71">
         <v>507</v>
       </c>
-      <c r="AC7" s="70">
+      <c r="AC7" s="73">
         <v>391</v>
       </c>
-      <c r="AD7" s="72">
+      <c r="AD7" s="75">
         <v>349</v>
       </c>
-      <c r="AE7" s="74">
+      <c r="AE7" s="77">
         <v>316</v>
       </c>
-      <c r="AF7" s="76">
+      <c r="AF7" s="79">
         <v>210</v>
       </c>
-      <c r="AG7" s="78">
+      <c r="AG7" s="81">
         <v>102</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>TOTAL PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="26">
         <v>41674</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="28">
         <v>40545</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="30">
         <v>15873</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="32">
         <v>13723</v>
       </c>
-      <c r="I8" s="31">
+      <c r="I8" s="34">
         <v>11501</v>
       </c>
-      <c r="J8" s="33">
+      <c r="J8" s="36">
         <v>11184</v>
       </c>
-      <c r="K8" s="35">
+      <c r="K8" s="38">
         <v>9518</v>
       </c>
-      <c r="L8" s="37">
+      <c r="L8" s="40">
         <v>7528</v>
       </c>
-      <c r="M8" s="39">
+      <c r="M8" s="42">
         <v>6570</v>
       </c>
-      <c r="N8" s="41">
+      <c r="N8" s="44">
         <v>4315</v>
       </c>
-      <c r="O8" s="43">
+      <c r="O8" s="46">
         <v>2007</v>
       </c>
-      <c r="P8" s="45">
+      <c r="P8" s="48">
         <v>8138</v>
       </c>
-      <c r="Q8" s="47">
+      <c r="Q8" s="50">
         <v>7058</v>
       </c>
-      <c r="R8" s="49">
+      <c r="R8" s="52">
         <v>5824</v>
       </c>
-      <c r="S8" s="51">
+      <c r="S8" s="54">
         <v>5626</v>
       </c>
-      <c r="T8" s="53">
+      <c r="T8" s="56">
         <v>4850</v>
       </c>
-      <c r="U8" s="55">
+      <c r="U8" s="58">
         <v>3745</v>
       </c>
-      <c r="V8" s="57">
+      <c r="V8" s="60">
         <v>3376</v>
       </c>
-      <c r="W8" s="59">
+      <c r="W8" s="62">
         <v>2091</v>
       </c>
-      <c r="X8" s="61">
+      <c r="X8" s="64">
         <v>966</v>
       </c>
-      <c r="Y8" s="63">
+      <c r="Y8" s="66">
         <v>7735</v>
       </c>
-      <c r="Z8" s="65">
+      <c r="Z8" s="68">
         <v>6665</v>
       </c>
-      <c r="AA8" s="67">
+      <c r="AA8" s="70">
         <v>5677</v>
       </c>
-      <c r="AB8" s="69">
+      <c r="AB8" s="72">
         <v>5558</v>
       </c>
-      <c r="AC8" s="71">
+      <c r="AC8" s="74">
         <v>4668</v>
       </c>
-      <c r="AD8" s="73">
+      <c r="AD8" s="76">
         <v>3783</v>
       </c>
-      <c r="AE8" s="75">
+      <c r="AE8" s="78">
         <v>3194</v>
       </c>
-      <c r="AF8" s="77">
+      <c r="AF8" s="80">
         <v>2224</v>
       </c>
-      <c r="AG8" s="79">
+      <c r="AG8" s="82">
         <v>1041</v>
       </c>
     </row>
@@ -2196,47 +2334,47 @@
   <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="73.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="24.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="74.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="25.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="84" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="84" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="84" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="84" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="84" t="inlineStr">
         <is>
           <t>Tasa de Natalidad</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="84" t="inlineStr">
         <is>
           <t>Tasa de Mortalidad</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="84" t="inlineStr">
         <is>
           <t>Índice de Envejecimiento</t>
         </is>
@@ -2261,14 +2399,14 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E2" s="80">
+      <c r="E2" s="86">
         <v>5.39180445722502</v>
       </c>
-      <c r="F2" s="82">
+      <c r="F2" s="88">
         <v>4.98220640569395</v>
       </c>
-      <c r="G2" s="84">
-        <v>34.9656357388316</v>
+      <c r="G2" s="90">
+        <v>33.8541679382324</v>
       </c>
     </row>
     <row r="3">
@@ -2290,14 +2428,14 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E3" s="80">
+      <c r="E3" s="86">
         <v>9.37700706486834</v>
       </c>
-      <c r="F3" s="82">
+      <c r="F3" s="88">
         <v>5.39499036608863</v>
       </c>
-      <c r="G3" s="84">
-        <v>33.2951781370725</v>
+      <c r="G3" s="90">
+        <v>30.7151584625244</v>
       </c>
     </row>
     <row r="4">
@@ -2319,14 +2457,14 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E4" s="80">
+      <c r="E4" s="86">
         <v>9.42275390224917</v>
       </c>
-      <c r="F4" s="82">
+      <c r="F4" s="88">
         <v>4.98965559206523</v>
       </c>
-      <c r="G4" s="84">
-        <v>19.8934280639432</v>
+      <c r="G4" s="90">
+        <v>19.5403366088867</v>
       </c>
     </row>
     <row r="5">
@@ -2348,14 +2486,14 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E5" s="80">
+      <c r="E5" s="86">
         <v>7.87474522883083</v>
       </c>
-      <c r="F5" s="82">
+      <c r="F5" s="88">
         <v>4.74304660158409</v>
       </c>
-      <c r="G5" s="84">
-        <v>24.7026251025431</v>
+      <c r="G5" s="90">
+        <v>24.1762981414795</v>
       </c>
     </row>
     <row r="6">
@@ -2377,14 +2515,14 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E6" s="80">
+      <c r="E6" s="86">
         <v>7.31112916328189</v>
       </c>
-      <c r="F6" s="82">
+      <c r="F6" s="88">
         <v>3.77877018206802</v>
       </c>
-      <c r="G6" s="84">
-        <v>27.1501752493934</v>
+      <c r="G6" s="90">
+        <v>24.6488208770752</v>
       </c>
     </row>
     <row r="7">
@@ -2406,107 +2544,107 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E7" s="80">
+      <c r="E7" s="86">
         <v>7.76038121170865</v>
       </c>
-      <c r="F7" s="82">
+      <c r="F7" s="88">
         <v>4.72589792060491</v>
       </c>
-      <c r="G7" s="84">
-        <v>28.2777950794145</v>
+      <c r="G7" s="90">
+        <v>25.648063659668</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="85" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE (por población)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E8" s="81">
+      <c r="E8" s="87">
         <v>8.4773483730043</v>
       </c>
-      <c r="F8" s="83">
+      <c r="F8" s="89">
         <v>4.84512611465422</v>
       </c>
-      <c r="G8" s="85">
-        <v>25.8194658390889</v>
+      <c r="G8" s="91">
+        <v>24.5269112436692</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="85" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E9" s="81">
+      <c r="E9" s="87">
         <v>8.34133878260628</v>
       </c>
-      <c r="F9" s="83">
+      <c r="F9" s="89">
         <v>4.90402610078376</v>
       </c>
-      <c r="G9" s="85">
-        <v>30.2492370183753</v>
+      <c r="G9" s="91">
+        <v>28.6236767503016</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="85" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="85" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E10" s="81">
+      <c r="E10" s="87">
         <v>8.63819084562528</v>
       </c>
-      <c r="F10" s="83">
+      <c r="F10" s="89">
         <v>5.63888092494404</v>
       </c>
-      <c r="G10" s="85">
-        <v>32.052654940463</v>
+      <c r="G10" s="91">
+        <v>31.7311728877886</v>
       </c>
     </row>
   </sheetData>
@@ -2521,47 +2659,47 @@
   <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="73.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="38.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="30.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="43.711"/>
-    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="49.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="74.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="39.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="31.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="44.711"/>
+    <col min="7" max="7" bestFit="1" customWidth="1" hidden="false" width="50.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="93" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="93" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="93" t="inlineStr">
         <is>
           <t>Subregión</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="93" t="inlineStr">
         <is>
           <t>Provincia</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="93" t="inlineStr">
         <is>
           <t>Tasa neta de migración - total</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="93" t="inlineStr">
         <is>
           <t>Tasa neta de migración - cabecera municipal</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="93" t="inlineStr">
         <is>
           <t>Tasa neta de migración - centros poblados y rural</t>
         </is>
@@ -2586,13 +2724,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E2" s="86">
+      <c r="E2" s="95">
         <v>2.17939692596504</v>
       </c>
-      <c r="F2" s="88">
+      <c r="F2" s="97">
         <v>2.94858870967742</v>
       </c>
-      <c r="G2" s="90">
+      <c r="G2" s="99">
         <v>1.76672074995493</v>
       </c>
     </row>
@@ -2615,13 +2753,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E3" s="86">
+      <c r="E3" s="95">
         <v>0</v>
       </c>
-      <c r="F3" s="88">
+      <c r="F3" s="97">
         <v>0</v>
       </c>
-      <c r="G3" s="90">
+      <c r="G3" s="99">
         <v>0</v>
       </c>
     </row>
@@ -2644,13 +2782,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E4" s="86">
+      <c r="E4" s="95">
         <v>0.0948640111580588</v>
       </c>
-      <c r="F4" s="88">
+      <c r="F4" s="97">
         <v>0</v>
       </c>
-      <c r="G4" s="90">
+      <c r="G4" s="99">
         <v>0.167681821477776</v>
       </c>
     </row>
@@ -2673,13 +2811,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E5" s="86">
+      <c r="E5" s="95">
         <v>0.992470595451687</v>
       </c>
-      <c r="F5" s="88">
+      <c r="F5" s="97">
         <v>0</v>
       </c>
-      <c r="G5" s="90">
+      <c r="G5" s="99">
         <v>1.87219763371807</v>
       </c>
     </row>
@@ -2702,13 +2840,13 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E6" s="86">
+      <c r="E6" s="95">
         <v>0</v>
       </c>
-      <c r="F6" s="88">
+      <c r="F6" s="97">
         <v>0</v>
       </c>
-      <c r="G6" s="90">
+      <c r="G6" s="99">
         <v>0</v>
       </c>
     </row>
@@ -2731,106 +2869,106 @@
           <t>PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE</t>
         </is>
       </c>
-      <c r="E7" s="86">
+      <c r="E7" s="95">
         <v>2.58074634652086</v>
       </c>
-      <c r="F7" s="88">
+      <c r="F7" s="97">
         <v>0.376157407407407</v>
       </c>
-      <c r="G7" s="90">
+      <c r="G7" s="99">
         <v>3.8178744110764</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="94" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO PROVINCIA AGROINDUSTRIAL DEL OCCIDENTE (por población)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E8" s="87">
+      <c r="E8" s="96">
         <v>0.608192875475374</v>
       </c>
-      <c r="F8" s="89">
+      <c r="F8" s="98">
         <v>0.136633070040527</v>
       </c>
-      <c r="G8" s="91">
+      <c r="G8" s="100">
         <v>0.966140685253155</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="94" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO SUBREGIÓN OCCIDENTE (por población)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E9" s="87">
+      <c r="E9" s="96">
         <v>1.36963640191563</v>
       </c>
-      <c r="F9" s="89">
+      <c r="F9" s="98">
         <v>0.910301066336893</v>
       </c>
-      <c r="G9" s="91">
+      <c r="G9" s="100">
         <v>1.65713154831215</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="94" t="inlineStr">
         <is>
           <t>PROMEDIO PONDERADO DEPARTAMENTO (ANTIOQUIA) (por población)</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="94" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E10" s="87">
+      <c r="E10" s="96">
         <v>2.43784156596946</v>
       </c>
-      <c r="F10" s="89">
+      <c r="F10" s="98">
         <v>2.2991539975123</v>
       </c>
-      <c r="G10" s="91">
+      <c r="G10" s="100">
         <v>2.88568680338064</v>
       </c>
     </row>
@@ -2846,23 +2984,23 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="102" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="102" t="inlineStr">
         <is>
           <t>habitantes_total</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="102" t="inlineStr">
         <is>
           <t>part_total_prov</t>
         </is>
@@ -2958,35 +3096,35 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="104" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="104" t="inlineStr">
         <is>
           <t>habitantes_cabecera</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="104" t="inlineStr">
         <is>
           <t>pct_cabecera</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="104" t="inlineStr">
         <is>
           <t>habitantes_rural</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="104" t="inlineStr">
         <is>
           <t>pct_rural</t>
         </is>
@@ -3118,22 +3256,23 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="13.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="106" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="106" t="inlineStr">
         <is>
           <t>habitantes_total</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="106" t="inlineStr">
         <is>
           <t>densidad_pob</t>
         </is>
@@ -3229,23 +3368,23 @@
   <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="108" t="inlineStr">
         <is>
           <t>banda</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="108" t="inlineStr">
         <is>
           <t>sexo</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="108" t="inlineStr">
         <is>
           <t>personas</t>
         </is>
@@ -3533,17 +3672,17 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="110" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="110" t="inlineStr">
         <is>
           <t>I_enve_T</t>
         </is>
@@ -3556,7 +3695,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>34.9656357388316</v>
+        <v>33.8541679382324</v>
       </c>
     </row>
     <row r="3">
@@ -3566,7 +3705,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>33.2951781370725</v>
+        <v>30.7151584625244</v>
       </c>
     </row>
     <row r="4">
@@ -3576,7 +3715,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>19.8934280639432</v>
+        <v>19.5403366088867</v>
       </c>
     </row>
     <row r="5">
@@ -3586,7 +3725,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>24.7026251025431</v>
+        <v>24.1762981414795</v>
       </c>
     </row>
     <row r="6">
@@ -3596,7 +3735,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>27.1501752493934</v>
+        <v>24.6488208770752</v>
       </c>
     </row>
     <row r="7">
@@ -3606,7 +3745,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>28.2777950794145</v>
+        <v>25.648063659668</v>
       </c>
     </row>
   </sheetData>
